--- a/Samples/Sample_Arabic_Invoice.xlsx
+++ b/Samples/Sample_Arabic_Invoice.xlsx
@@ -57,9 +57,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="50" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -68,9 +70,12 @@
           <t>Tripack</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>كشف حساب المبيعات والفواتير - لشهر أكتوبر 2026</t>
+      <c r="C1" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>كشف حساب المبيعات والفواتير - لشهر أكتوبر</t>
         </is>
       </c>
     </row>
@@ -80,12 +85,12 @@
           <t>Report No: INV-2026-108</t>
         </is>
       </c>
-      <c r="B2" s="0" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>Date: 2026-10-20</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>الفرع الرئيسي - الرياض</t>
         </is>
@@ -94,215 +99,279 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>التاريخ رقم الفاتورة</t>
+          <t>رقم الفاتورة</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
           <t>اسم العميل</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>الكمية البيان / الصنف</t>
-        </is>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>البيان / الصنف</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>الكمية</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t>10041 2026-10-01</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" s="0">
+        <v>10041</v>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>شركة الأمل للتجارة</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>12 أجهزة حاسب مكتبي</t>
-        </is>
-      </c>
-      <c r="D4" s="0">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>أجهزة حاسب مكتبي</t>
+        </is>
+      </c>
+      <c r="E4" s="0">
+        <v>12</v>
+      </c>
+      <c r="F4" s="0">
         <v>28500</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t>10042 2026-10-03</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="A5" s="0">
+        <v>10042</v>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>مؤسسة النهضة الحديثة</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>5 طابعات ليزر ملونة</t>
-        </is>
-      </c>
-      <c r="D5" s="0">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>طابعات ليزر ملونة</t>
+        </is>
+      </c>
+      <c r="E5" s="0">
+        <v>5</v>
+      </c>
+      <c r="F5" s="0">
         <v>7250.5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>10043 2026-10-05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="A6" s="0">
+        <v>10043</v>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>مستشفى الشفاء التخصصي</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2 خوادم شبكات رئيسية</t>
-        </is>
-      </c>
-      <c r="D6" s="0">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>خوادم شبكات رئيسية</t>
+        </is>
+      </c>
+      <c r="E6" s="0">
+        <v>2</v>
+      </c>
+      <c r="F6" s="0">
         <v>44000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t>10044 2026-10-08</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="A7" s="0">
+        <v>10044</v>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>شركة الخليج للمقاولات</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>8 شاشات عرض تفاعلية</t>
-        </is>
-      </c>
-      <c r="D7" s="0">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>شاشات عرض تفاعلية</t>
+        </is>
+      </c>
+      <c r="E7" s="0">
+        <v>8</v>
+      </c>
+      <c r="F7" s="0">
         <v>15600.75</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t>10045 2026-10-11</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="A8" s="0">
+        <v>10045</v>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>مكتبة المعرفة الكبرى</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>15 برمجيات محاسبة ومخازن</t>
-        </is>
-      </c>
-      <c r="D8" s="0">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>برمجيات محاسبة ومخازن</t>
+        </is>
+      </c>
+      <c r="E8" s="0">
+        <v>15</v>
+      </c>
+      <c r="F8" s="0">
         <v>22500</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t>10046 2026-10-14</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="A9" s="0">
+        <v>10046</v>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>مجموعة الفيصل الصناعية</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>10 يطايتحا نيزخت تادحو</t>
-        </is>
-      </c>
-      <c r="D9" s="0">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>وحدات تخزين احتياطي</t>
+        </is>
+      </c>
+      <c r="E9" s="0">
+        <v>10</v>
+      </c>
+      <c r="F9" s="0">
         <v>13400</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t>10047 2026-10-17</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="A10" s="0">
+        <v>10047</v>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>شركة الشرق الأوسط</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1 عقود صيانة سنوية</t>
-        </is>
-      </c>
-      <c r="D10" s="0">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>عقود صيانة سنوية</t>
+        </is>
+      </c>
+      <c r="E10" s="0">
+        <v>1</v>
+      </c>
+      <c r="F10" s="0">
         <v>18000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t>10048 2026-10-19</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="A11" s="0">
+        <v>10048</v>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>مؤسسة البناء المتطور</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>40 طبر تادعمو تالباك</t>
-        </is>
-      </c>
-      <c r="D11" s="0">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>كابلات ومعدات ربط</t>
+        </is>
+      </c>
+      <c r="E11" s="0">
+        <v>40</v>
+      </c>
+      <c r="F11" s="0">
         <v>6800.25</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t>10049 2026-10-20</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="A12" s="0">
+        <v>10049</v>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>مركز الإبداع التقني</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>25 أجهزة قارئ باركود</t>
-        </is>
-      </c>
-      <c r="D12" s="0">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>أجهزة قارئ باركود</t>
+        </is>
+      </c>
+      <c r="E12" s="0">
+        <v>25</v>
+      </c>
+      <c r="F12" s="0">
         <v>9375</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>المجموع الكليTOTAL /</t>
         </is>
       </c>
-      <c r="C13" s="1">
+      <c r="E13" s="1">
         <v>118</v>
       </c>
-      <c r="D13" s="1">
+      <c r="F13" s="1">
         <v>165426.5</v>
       </c>
     </row>
@@ -312,7 +381,7 @@
           <t>اعتمد من قبل الإدارة المالية - توقيع المحاسب</t>
         </is>
       </c>
-      <c r="C14" s="0" t="inlineStr">
+      <c r="F14" s="0" t="inlineStr">
         <is>
           <t>Page 1 of 1</t>
         </is>
